--- a/Result/profitability/4128.xlsx
+++ b/Result/profitability/4128.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>-0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3825</v>
+        <v>-0.12</v>
       </c>
       <c r="N2" t="n">
-        <v>40.735</v>
+        <v>40.4575</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.22875</v>
+        <v>0.01500000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>39.3425</v>
+        <v>39.01875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.17</v>
+        <v>0.06000000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>39.43875</v>
+        <v>39.35125</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1175</v>
+        <v>0.14125</v>
       </c>
       <c r="N5" t="n">
-        <v>38.37875</v>
+        <v>38.23999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05999999999999994</v>
+        <v>0.13625</v>
       </c>
       <c r="N6" t="n">
-        <v>38.435</v>
+        <v>38.29875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05499999999999994</v>
+        <v>0.13</v>
       </c>
       <c r="N7" t="n">
-        <v>38.86125000000001</v>
+        <v>38.26375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.10375</v>
+        <v>0.1125</v>
       </c>
       <c r="N8" t="n">
-        <v>38.8775</v>
+        <v>38.7225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>0.06</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05749999999999994</v>
+        <v>-0.05749999999999995</v>
       </c>
       <c r="N9" t="n">
         <v>40.475</v>
@@ -1649,7 +1649,7 @@
         <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02250000000000006</v>
+        <v>0.02250000000000005</v>
       </c>
       <c r="N10" t="n">
         <v>40.99125</v>
@@ -1776,7 +1776,7 @@
         <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03124999999999994</v>
+        <v>-0.03124999999999995</v>
       </c>
       <c r="N11" t="n">
         <v>44.31375</v>
@@ -1906,7 +1906,7 @@
         <v>-0.03249999999999995</v>
       </c>
       <c r="N12" t="n">
-        <v>45.68125</v>
+        <v>45.68125000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>479</v>
+      </c>
+      <c r="D75" t="n">
+        <v>298</v>
+      </c>
+      <c r="E75" t="n">
+        <v>181</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-32.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>903</v>
+      </c>
+      <c r="J75" t="n">
+        <v>750</v>
+      </c>
+      <c r="K75" t="n">
+        <v>832</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.49625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-5.580645161290322</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.240000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03177857508969761</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.184615384615384</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.109999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02854204165595264</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
